--- a/practice/answers/s1_q24.xlsx
+++ b/practice/answers/s1_q24.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,32 +76,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,195 +463,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ROUND changes the value; formatting changes the look</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The same five yields shown two ways. The proof of the difference is that the two columns total differently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Plot</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Yield (stored)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Yield (formatted)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ROUND to 1 dp</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Yield (ROUND, 1 dp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Plot 1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="3" t="n">
         <v>42.47</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C2" s="4">
+        <f>ROUND(B2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Plot 2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="C3" s="4">
+        <f>ROUND(B3,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Plot 3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="C4" s="4">
+        <f>ROUND(B4,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Plot 4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="C5" s="4">
         <f>ROUND(B5,1)</f>
         <v/>
       </c>
-      <c r="E5" s="9">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Plot 2</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="D6" s="8">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Plot 5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="C6" s="4">
         <f>ROUND(B6,1)</f>
         <v/>
       </c>
-      <c r="E6" s="9">
-        <f>_xlfn.FORMULATEXT(D6)</f>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>SUM(B2:B6)</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Plot 3</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="D7" s="8">
-        <f>ROUND(B7,1)</f>
+      <c r="C7" s="6">
+        <f>SUM(C2:C6)</f>
         <v/>
       </c>
-      <c r="E7" s="9">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Plot 4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="D8" s="8">
-        <f>ROUND(B8,1)</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Plot 5</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="D9" s="8">
-        <f>ROUND(B9,1)</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>_xlfn.FORMULATEXT(D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="11">
-        <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Columns B and C hold identical values and display differently; both total 218.04. Column D holds different values and totals 218.10. A formatted column shows numbers that do not add up to its own total, which reads as an error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Formatted to one decimal, the original column would display 42.5, 38.9, 51.3, 45.6, 39.8 -- the same as the rounded column -- but its total would still read 218.04, because the stored values never change. The column here keeps its full display.</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ROUND changed the stored values; formatting changes only their appearance. The totals are the proof: the original column adds to 218.04 while a one-decimal display would show numbers that add to 218.1.</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Use ROUND, so the values really are what the reader sees and the total is the sum of those values. A formatted column shows one thing and totals another, which reads as an arithmetic error.</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="3">
+    <mergeCell ref="A13:G15"/>
+    <mergeCell ref="A17:G19"/>
+    <mergeCell ref="A9:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q24.xlsx
+++ b/practice/answers/s1_q24.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -31,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +56,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,28 +69,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,253 +444,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Yield (ROUND, 1 dp)</t>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Peas</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Field total (a)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>All acres (c)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Plot 1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="C2" s="4">
-        <f>ROUND(B2,1)</f>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>320</v>
+      </c>
+      <c r="C2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2">
+        <f>SUM(B2:D2)</f>
+        <v/>
+      </c>
+      <c r="G2" s="3">
+        <f>SUM(B2:D6)</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Plot 2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="C3" s="4">
-        <f>ROUND(B3,1)</f>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C3" t="n">
+        <v>320</v>
+      </c>
+      <c r="D3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E3" s="2">
+        <f>SUM(B3:D3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plot 3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="C4" s="4">
-        <f>ROUND(B4,1)</f>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>240</v>
+      </c>
+      <c r="C4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="2">
+        <f>SUM(B4:D4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Plot 4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="C5" s="4">
-        <f>ROUND(B5,1)</f>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>160</v>
+      </c>
+      <c r="C5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2">
+        <f>SUM(B5:D5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Plot 5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="C6" s="4">
-        <f>ROUND(B6,1)</f>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>160</v>
+      </c>
+      <c r="D6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E6" s="2">
+        <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Crop total (b)</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
         <f>SUM(B2:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <f>SUM(C2:C6)</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Formatted to one decimal, the original column would display 42.5, 38.9, 51.3, 45.6, 39.8 -- the same as the rounded column -- but its total would still read 218.04, because the stored values never change. The column here keeps its full display.</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="D7" s="4">
+        <f>SUM(D2:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>(d) =SUM(B2:B6, D2:D6) adds only the Canola and Peas columns -- 1,560 acres. It misses every Wheat acre (column C, 960 acres), because the two arguments name two column ranges and skip the column between them.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>ROUND changed the stored values; formatting changes only their appearance. The totals are the proof: the original column adds to 218.04 while a one-decimal display would show numbers that add to 218.1.</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Use ROUND, so the values really are what the reader sees and the total is the sum of those values. A formatted column shows one thing and totals another, which reads as an arithmetic error.</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Part (d)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A13:G15"/>
-    <mergeCell ref="A17:G19"/>
-    <mergeCell ref="A9:G11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q24.xlsx
+++ b/practice/answers/s1_q24.xlsx
@@ -610,7 +610,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>(d) =SUM(B2:B6, D2:D6) adds only the Canola and Peas columns -- 1,560 acres. It misses every Wheat acre (column C, 960 acres), because the two arguments name two column ranges and skip the column between them.</t>

--- a/practice/answers/s1_q24.xlsx
+++ b/practice/answers/s1_q24.xlsx
@@ -73,8 +73,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -444,15 +444,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,11 +480,6 @@
           <t>Field total (a)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>All acres (c)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -506,10 +500,6 @@
         <f>SUM(B2:D2)</f>
         <v/>
       </c>
-      <c r="G2" s="3">
-        <f>SUM(B2:D6)</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -597,56 +587,67 @@
           <t>Crop total (b)</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <f>SUM(B2:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <f>SUM(C2:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <f>SUM(D2:D6)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>All acres (c)</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>SUM(B2:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>(d) =SUM(B2:B6, D2:D6) adds only the Canola and Peas columns -- 1,560 acres. It misses every Wheat acre (column C, 960 acres), because the two arguments name two column ranges and skip the column between them.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Legend: colours mark question parts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Part (a)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Part (b)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Part (c)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Part (d)</t>
         </is>
@@ -654,7 +655,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q24.xlsx
+++ b/practice/answers/s1_q24.xlsx
@@ -1,59 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D9827905596FF60075C9657D0D67C890EF46A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F734B54-0B79-4C28-9552-714F9E747CA0}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Peas</t>
+  </si>
+  <si>
+    <t>Field total (a)</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Creek</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Rented</t>
+  </si>
+  <si>
+    <t>Crop total (b)</t>
+  </si>
+  <si>
+    <t>All acres (c)</t>
+  </si>
+  <si>
+    <t>(d) =SUM(B2:B6, D2:D6) adds only the Canola and Peas columns -- 1,560 acres. It misses every Wheat acre (column C, 960 acres), because the two arguments name two column ranges and skip the column between them.</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,89 +145,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -439,218 +457,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Peas</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Field total (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <v>320</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>160</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>80</v>
       </c>
       <c r="E2" s="2">
         <f>SUM(B2:D2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>160</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>320</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>160</v>
       </c>
       <c r="E3" s="2">
         <f>SUM(B3:D3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Creek</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>240</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>80</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>120</v>
       </c>
       <c r="E4" s="2">
         <f>SUM(B4:D4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>160</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>240</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>80</v>
       </c>
       <c r="E5" s="2">
         <f>SUM(B5:D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rented</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>80</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>160</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>160</v>
       </c>
       <c r="E6" s="2">
         <f>SUM(B6:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Crop total (b)</t>
-        </is>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(B2:B6)</f>
-        <v/>
+        <v>960</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(C2:C6)</f>
-        <v/>
+        <v>960</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(D2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>All acres (c)</t>
-        </is>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(B2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>(d) =SUM(B2:B6, D2:D6) adds only the Canola and Peas columns -- 1,560 acres. It misses every Wheat acre (column C, 960 acres), because the two arguments name two column ranges and skip the column between them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="63.95" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
